--- a/Data IKPA KPPN/2025/IKPA_KPPN_DESEMBER_2025.xlsx
+++ b/Data IKPA KPPN/2025/IKPA_KPPN_DESEMBER_2025.xlsx
@@ -550,76 +550,54 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>97.73</v>
+      </c>
+      <c r="F2" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="G2" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="M2" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>99,71</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>92,19</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>94,26</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>96,66</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>98,44</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>97,50</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>100,00%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>DESEMBER</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="S2" t="n">
+        <v>2025</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
